--- a/public/templates/智育成绩单模板.xlsx
+++ b/public/templates/智育成绩单模板.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成绩单模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,17 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,7 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,427 +417,1042 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>院系</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>专业</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>年级</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>学生类别</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>校区</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>班级</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>学习形式</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>学号</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>学号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>专业</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>年级</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>班级</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>学年</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>学期</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>课程号</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>主讲教师</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>总评</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>绩点</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>学分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>总评</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>考试性质</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>缓考</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>是否缓考</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>课程类别</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>及格标志</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>成绩录入人用户名</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>成绩录入人姓名</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5231921401</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5231921401</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>智能制造工程（本）</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2023级</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>智造23-本4班</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>高等数学B</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>88</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>B21C002511</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>机械制造工艺</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>赵琳</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>85</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>专业核心课</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5231921401</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>5231921401</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>智能制造工程（本）</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2023级</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>智造23-本4班</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>大学英语（一）</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>B21C002512</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>机械控制工程基础</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>82</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>专业核心课</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5231921401</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5231921401</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>智能制造工程（本）</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2023级</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>智造23-本4班</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>形势与政策（5）</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>85</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>B21C002513</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Python程序设计</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>李芳</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>78</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>专业基础课</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>机械与控制工程学院</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5231921402</t>
+          <t>智能制造工程（本）</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>智能制造工程（本）</t>
+          <t>2023级</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2023级</t>
+          <t>本科(本科)4年</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>智造23-本4班</t>
+          <t>空港校区</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5231921401</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>B21C002514</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>高等数学B</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="n">
-        <v>77</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>公共基础课</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5231921402</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5231921402</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>智能制造工程（本）</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2023级</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>智造23-本4班</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>大学英语（一）</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>B21C002511</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>机械制造工艺</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>赵琳</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>79</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>90</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>专业核心课</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5231921402</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>B21C002512</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>机械控制工程基础</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>专业核心课</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>5231921402</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>智能制造工程（本）</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2023级</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>智造23-本4班</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>B21C002513</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Python程序设计</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>李芳</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>90</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>专业基础课</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>机械与控制工程学院</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>智能制造工程（本）</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>总评支持分数或等级：优/良/中/及格/不及格/合格；考试性质可填：正常/补考/重修/缓考/免修；</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>挂科后补考通过仍按补考前的原始分数计（第16条）；重修课程不计入智育（第15条）；</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>缓考按缓考成绩计；作弊/缺考按0分；等级换算：优95/良85/中75/及格65/不及格40/合格65；体育免修按65。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>2023级</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>本科(本科)4年</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>空港校区</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>智造23-本4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>普通全日制</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5231921402</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>B21C002514</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>高等数学B</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>72</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>正常考试</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>公共基础课</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>9814043</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>模板数据</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
